--- a/src/reports/template.xlsx
+++ b/src/reports/template.xlsx
@@ -966,7 +966,7 @@
       <c r="C39" s="24" t="n"/>
       <c r="D39" s="24" t="n"/>
       <c r="E39" s="6">
-        <f>SUM(D4:D7)</f>
+        <f>SUM(D4:D37)</f>
         <v/>
       </c>
     </row>
